--- a/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigS4_distribution_construct_ablation_source_data.xlsx
+++ b/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigS4_distribution_construct_ablation_source_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,10 +476,20 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>n_process_time_blocks</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>bootstrap_unit</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>decision_scope</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>calibration_id</t>
         </is>
@@ -511,22 +521,30 @@
         <v>0.0007243638196019475</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.008851410934744263</v>
+        <v>-0.009888815873015881</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01219844419249181</v>
+        <v>0.01211432387174971</v>
       </c>
       <c r="I2" t="n">
         <v>126</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>internal_validation_construct_ablation</t>
-        </is>
+      <c r="J2" t="n">
+        <v>11</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>internal_validation_construct_ablation</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -556,22 +574,30 @@
         <v>-0.0046555341294372</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.01956212558739268</v>
+        <v>-0.02014352457163186</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006988356066517341</v>
+        <v>0.007405756463057225</v>
       </c>
       <c r="I3" t="n">
         <v>126</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>internal_validation_construct_ablation</t>
-        </is>
+      <c r="J3" t="n">
+        <v>11</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>internal_validation_construct_ablation</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -601,22 +627,30 @@
         <v>-0.02900604686318964</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.04658210506424795</v>
+        <v>-0.04338726065367482</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.01035761526832962</v>
+        <v>-0.009099450753671528</v>
       </c>
       <c r="I4" t="n">
         <v>126</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>internal_validation_construct_ablation</t>
-        </is>
+      <c r="J4" t="n">
+        <v>11</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>internal_validation_construct_ablation</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -646,22 +680,30 @@
         <v>-0.03305976176393211</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.05420793632602738</v>
+        <v>-0.04450890500041616</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.01647205103244303</v>
+        <v>-0.01580330163232557</v>
       </c>
       <c r="I5" t="n">
         <v>126</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>internal_validation_construct_ablation</t>
-        </is>
+      <c r="J5" t="n">
+        <v>11</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>internal_validation_construct_ablation</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -691,22 +733,30 @@
         <v>-0.009353741496598622</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.01965939153439158</v>
+        <v>-0.02425687741423761</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001199924414210088</v>
+        <v>0.005300738543907021</v>
       </c>
       <c r="I6" t="n">
         <v>126</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>internal_validation_construct_ablation</t>
-        </is>
+      <c r="J6" t="n">
+        <v>11</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>internal_validation_construct_ablation</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -736,22 +786,30 @@
         <v>-0.02264309810515686</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.04300079759379202</v>
+        <v>-0.0489486185550975</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.00644027073600072</v>
+        <v>-0.004112169951507827</v>
       </c>
       <c r="I7" t="n">
         <v>126</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>internal_validation_construct_ablation</t>
-        </is>
+      <c r="J7" t="n">
+        <v>11</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>internal_validation_construct_ablation</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -781,22 +839,30 @@
         <v>0.01521164021164023</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.002177028218694876</v>
+        <v>-0.003813559322033882</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03159643487024445</v>
+        <v>0.03038722915636836</v>
       </c>
       <c r="I8" t="n">
         <v>126</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>internal_validation_construct_ablation</t>
-        </is>
+      <c r="J8" t="n">
+        <v>11</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>internal_validation_construct_ablation</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -826,22 +892,30 @@
         <v>0.009675489341721466</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.006379989119018367</v>
+        <v>-0.003930731918453778</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02439408152770203</v>
+        <v>0.01972707033827111</v>
       </c>
       <c r="I9" t="n">
         <v>126</v>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>internal_validation_construct_ablation</t>
-        </is>
+      <c r="J9" t="n">
+        <v>11</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>internal_validation_construct_ablation</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -871,22 +945,30 @@
         <v>-0.03162005542957924</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.04831664147140341</v>
+        <v>-0.0455966465178466</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.01697452128999745</v>
+        <v>-0.01566311011687342</v>
       </c>
       <c r="I10" t="n">
         <v>126</v>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>internal_validation_construct_ablation</t>
-        </is>
+      <c r="J10" t="n">
+        <v>11</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>internal_validation_construct_ablation</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -916,22 +998,30 @@
         <v>-0.02711366230336987</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.04597151155573733</v>
+        <v>-0.04668202999497939</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.01239815231249315</v>
+        <v>-0.01353422833350656</v>
       </c>
       <c r="I11" t="n">
         <v>126</v>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>internal_validation_construct_ablation</t>
-        </is>
+      <c r="J11" t="n">
+        <v>11</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>internal_validation_construct_ablation</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -961,22 +1051,30 @@
         <v>0.1266061980347695</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1024502393550013</v>
+        <v>0.1076053968647524</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1550311791383219</v>
+        <v>0.15010230147986</v>
       </c>
       <c r="I12" t="n">
         <v>126</v>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>internal_validation_construct_ablation</t>
-        </is>
+      <c r="J12" t="n">
+        <v>11</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>internal_validation_construct_ablation</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1006,22 +1104,30 @@
         <v>0.1069336179178364</v>
       </c>
       <c r="G13" t="n">
-        <v>0.08680101737714205</v>
+        <v>0.08734802984135182</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1300391636254031</v>
+        <v>0.1309442046575186</v>
       </c>
       <c r="I13" t="n">
         <v>126</v>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>internal_validation_construct_ablation</t>
-        </is>
+      <c r="J13" t="n">
+        <v>11</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>internal_validation_construct_ablation</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1051,22 +1157,30 @@
         <v>0.0185185185185186</v>
       </c>
       <c r="G14" t="n">
-        <v>0.005889392794154677</v>
+        <v>0.01004016051540963</v>
       </c>
       <c r="H14" t="n">
-        <v>0.03209719072814304</v>
+        <v>0.03024319336393431</v>
       </c>
       <c r="I14" t="n">
         <v>126</v>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>internal_validation_construct_ablation</t>
-        </is>
+      <c r="J14" t="n">
+        <v>11</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>internal_validation_construct_ablation</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1096,22 +1210,30 @@
         <v>0.01506275099019927</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.006506435676959313</v>
+        <v>0.006229950137381006</v>
       </c>
       <c r="H15" t="n">
-        <v>0.03588985724603083</v>
+        <v>0.02900409027641716</v>
       </c>
       <c r="I15" t="n">
         <v>126</v>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>internal_validation_construct_ablation</t>
-        </is>
+      <c r="J15" t="n">
+        <v>11</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>internal_validation_construct_ablation</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1141,22 +1263,30 @@
         <v>-0.03927311665406896</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0601481796422272</v>
+        <v>-0.05830076690293818</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.02002551020408156</v>
+        <v>-0.02191661956604886</v>
       </c>
       <c r="I16" t="n">
         <v>126</v>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>internal_validation_construct_ablation</t>
-        </is>
+      <c r="J16" t="n">
+        <v>11</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>internal_validation_construct_ablation</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1186,22 +1316,30 @@
         <v>-0.04084921124870766</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0634838962806982</v>
+        <v>-0.06702166410954616</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.02249439649611045</v>
+        <v>-0.02116650485713153</v>
       </c>
       <c r="I17" t="n">
         <v>126</v>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>internal_validation_construct_ablation</t>
-        </is>
+      <c r="J17" t="n">
+        <v>11</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>internal_validation_construct_ablation</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1230,19 +1368,27 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04547202797202796</v>
       </c>
       <c r="I18" t="n">
         <v>69</v>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" t="n">
+        <v>11</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>internal_validation_negative_control</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1271,19 +1417,27 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04617187499999999</v>
       </c>
       <c r="I19" t="n">
         <v>69</v>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" t="n">
+        <v>11</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>internal_validation_negative_control</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1309,22 +1463,30 @@
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>0.02898550724637681</v>
+        <v>0.03331967213114754</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1594202898550725</v>
+        <v>0.1528044871794872</v>
       </c>
       <c r="I20" t="n">
         <v>69</v>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" t="n">
+        <v>11</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>internal_validation_negative_control</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
